--- a/Students/BKS2501/BKS2501_Grade.xlsx
+++ b/Students/BKS2501/BKS2501_Grade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\МТУСИ\Введение в ИТ\БКС2501\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAE469B-B360-419A-9DDE-67831E9F8400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E81CC2-B66D-4B12-A600-1618A5C106D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="45">
   <si>
     <t>ФИО</t>
   </si>
@@ -189,7 +189,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -199,6 +199,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFAAE571"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -285,26 +291,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -319,7 +313,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -624,84 +636,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="8"/>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="10"/>
+      <c r="E1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="8"/>
-      <c r="G1" s="7" t="s">
+      <c r="F1" s="10"/>
+      <c r="G1" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="7" t="s">
+      <c r="H1" s="10"/>
+      <c r="I1" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="8"/>
-      <c r="K1" s="7" t="s">
+      <c r="J1" s="10"/>
+      <c r="K1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="8"/>
-      <c r="M1" s="7" t="s">
+      <c r="L1" s="10"/>
+      <c r="M1" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="N1" s="8"/>
-      <c r="O1" s="7" t="s">
+      <c r="N1" s="10"/>
+      <c r="O1" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="8"/>
+      <c r="P1" s="10"/>
     </row>
     <row r="2" spans="1:16" ht="18.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6" t="s">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="4" t="s">
         <v>37</v>
       </c>
     </row>
@@ -712,20 +724,24 @@
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
+      <c r="C3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
@@ -735,20 +751,24 @@
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
+      <c r="C4" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
@@ -758,20 +778,26 @@
       <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
+      <c r="C5" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
@@ -781,20 +807,20 @@
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
@@ -804,24 +830,28 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
+      <c r="C7" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
@@ -831,22 +861,22 @@
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
+      <c r="C8" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9" s="3">
@@ -854,22 +884,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
+        <v>9</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10" s="3">
@@ -877,49 +907,51 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
+        <v>10</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
+      <c r="B11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12" s="3">
@@ -927,22 +959,26 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
+        <v>12</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13" s="3">
@@ -950,22 +986,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
+        <v>13</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14" s="3">
@@ -973,49 +1009,55 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="12"/>
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16" s="3">
@@ -1023,22 +1065,24 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
+        <v>16</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
@@ -1046,22 +1090,26 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
+        <v>17</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A18" s="3">
@@ -1069,22 +1117,22 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
+        <v>18</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A19" s="3">
@@ -1092,72 +1140,88 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
+        <v>19</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A20" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
+      <c r="B20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A21" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
-      <c r="O21" s="12"/>
-      <c r="P21" s="12"/>
+      <c r="B21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A22" s="3">
@@ -1165,101 +1229,121 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
+        <v>22</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A23" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="10"/>
+      <c r="B23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A24" s="3">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
-      <c r="P24" s="12"/>
+      <c r="B24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A25" s="3">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
+      <c r="B25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A26" s="3">
@@ -1267,38 +1351,28 @@
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="12"/>
+        <v>26</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A27" s="3">
@@ -1306,22 +1380,26 @@
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
+        <v>34</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" s="7"/>
+      <c r="E27" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28" s="3">
@@ -1329,22 +1407,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12"/>
+        <v>27</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A29" s="3">
@@ -1352,22 +1430,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
+        <v>28</v>
+      </c>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="8"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30" s="3">
@@ -1375,22 +1453,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
+        <v>29</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="8"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31" s="3">
@@ -1398,22 +1476,22 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
+        <v>30</v>
+      </c>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
+      <c r="P31" s="8"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A32" s="3">
@@ -1421,22 +1499,26 @@
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="12"/>
-      <c r="P32" s="12"/>
+        <v>31</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
+      <c r="P32" s="8"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A33" s="3">
@@ -1444,24 +1526,22 @@
         <v>31</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="12"/>
-      <c r="P33" s="12"/>
+        <v>32</v>
+      </c>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
+      <c r="P33" s="8"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A34" s="3">
@@ -1469,45 +1549,45 @@
         <v>32</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="12"/>
-      <c r="P34" s="12"/>
+        <v>33</v>
+      </c>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="8"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A35" s="3">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
-      <c r="O35" s="12"/>
-      <c r="P35" s="12"/>
+      <c r="B35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
+      <c r="P35" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="9">
